--- a/prizmer/static/excel/heat_template_for_load.xlsx
+++ b/prizmer/static/excel/heat_template_for_load.xlsx
@@ -5,22 +5,17 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Web-prizmer\wui3\prizmer\static\cfg\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Web-prizmer\wui3\prizmer\static\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7CBBC4F-DF04-4097-84D1-C55E45806D72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{135604E8-1EA0-44C8-B542-53BE444206F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13860" yWindow="0" windowWidth="23640" windowHeight="17400" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Heat_1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0" iterateDelta="0"/>
-  <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
@@ -48,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="61">
   <si>
     <t>Населенный пункт</t>
   </si>
@@ -225,6 +220,12 @@
   </si>
   <si>
     <t>Sayany</t>
+  </si>
+  <si>
+    <t>Квартира 093</t>
+  </si>
+  <si>
+    <t>Пульсар Холодосчётчик</t>
   </si>
 </sst>
 </file>
@@ -234,7 +235,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="000"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -278,6 +279,10 @@
       <family val="2"/>
       <charset val="204"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -299,7 +304,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -359,12 +364,28 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -391,9 +412,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="4" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -417,12 +435,29 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="Обычный 2" xfId="2" xr:uid="{AC3BC87D-910B-4CD8-A453-B327BA67F137}"/>
     <cellStyle name="Обычный 8" xfId="1" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="4">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -644,7 +679,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AA17"/>
+  <dimension ref="A1:AA18"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" style="1" customWidth="1"/>
@@ -657,7 +692,7 @@
     <col min="9" max="9" width="26" style="1" customWidth="1"/>
     <col min="10" max="10" width="5.140625" style="1" customWidth="1"/>
     <col min="11" max="11" width="18.28515625" style="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" customWidth="1"/>
+    <col min="15" max="15" width="18.140625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="75" x14ac:dyDescent="0.25">
@@ -703,645 +738,685 @@
       <c r="N1" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="10" t="s">
+      <c r="O1" s="9" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A2" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" s="11" t="s">
+      <c r="A2" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12">
+      <c r="E2" s="11"/>
+      <c r="F2" s="11"/>
+      <c r="G2" s="11">
         <v>173456974</v>
       </c>
-      <c r="H2" s="12">
-        <v>1</v>
-      </c>
-      <c r="I2" s="12" t="s">
+      <c r="H2" s="11">
+        <v>1</v>
+      </c>
+      <c r="I2" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="J2" s="12">
-        <v>1</v>
-      </c>
-      <c r="K2" s="12" t="s">
+      <c r="J2" s="11">
+        <v>1</v>
+      </c>
+      <c r="K2" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="L2" s="12">
+      <c r="L2" s="11">
         <v>4001</v>
       </c>
-      <c r="M2" s="13"/>
-      <c r="N2" s="13"/>
-      <c r="O2" s="14"/>
+      <c r="M2" s="12"/>
+      <c r="N2" s="12"/>
+      <c r="O2" s="13"/>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A3" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" s="11" t="s">
+      <c r="A3" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="12"/>
-      <c r="F3" s="15"/>
-      <c r="G3" s="15">
+      <c r="E3" s="11"/>
+      <c r="F3" s="14"/>
+      <c r="G3" s="14">
         <v>655276</v>
       </c>
-      <c r="H3" s="15">
+      <c r="H3" s="14">
         <v>655276</v>
       </c>
-      <c r="I3" s="12" t="s">
+      <c r="I3" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="J3" s="12">
-        <v>1</v>
-      </c>
-      <c r="K3" s="12" t="s">
+      <c r="J3" s="11">
+        <v>1</v>
+      </c>
+      <c r="K3" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="L3" s="12">
+      <c r="L3" s="11">
         <v>4004</v>
       </c>
-      <c r="M3" s="13"/>
-      <c r="N3" s="13"/>
-      <c r="O3" s="14"/>
+      <c r="M3" s="12"/>
+      <c r="N3" s="12"/>
+      <c r="O3" s="13"/>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A4" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" s="12" t="s">
+      <c r="A4" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12" t="s">
+      <c r="E4" s="11"/>
+      <c r="F4" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="G4" s="12" t="s">
+      <c r="G4" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="H4" s="12">
+      <c r="H4" s="11">
         <v>46</v>
       </c>
-      <c r="I4" s="12" t="s">
+      <c r="I4" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="J4" s="12">
-        <v>1</v>
-      </c>
-      <c r="K4" s="16" t="s">
+      <c r="J4" s="11">
+        <v>1</v>
+      </c>
+      <c r="K4" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="L4" s="12">
+      <c r="L4" s="11">
         <v>4001</v>
       </c>
-      <c r="M4" s="13"/>
-      <c r="N4" s="13"/>
-      <c r="O4" s="14"/>
+      <c r="M4" s="12"/>
+      <c r="N4" s="12"/>
+      <c r="O4" s="13"/>
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A5" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="12" t="s">
+      <c r="A5" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="E5" s="12"/>
-      <c r="F5" s="12" t="s">
+      <c r="E5" s="11"/>
+      <c r="F5" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="G5" s="12" t="s">
+      <c r="G5" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="H5" s="12">
+      <c r="H5" s="11">
         <v>47</v>
       </c>
-      <c r="I5" s="12" t="s">
+      <c r="I5" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="J5" s="12">
-        <v>1</v>
-      </c>
-      <c r="K5" s="16" t="s">
+      <c r="J5" s="11">
+        <v>1</v>
+      </c>
+      <c r="K5" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="L5" s="12">
+      <c r="L5" s="11">
         <v>4001</v>
       </c>
-      <c r="M5" s="13"/>
-      <c r="N5" s="13"/>
-      <c r="O5" s="14"/>
+      <c r="M5" s="12"/>
+      <c r="N5" s="12"/>
+      <c r="O5" s="13"/>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A6" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" s="12" t="s">
+      <c r="A6" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12">
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11">
         <v>3472</v>
       </c>
-      <c r="H6" s="12">
+      <c r="H6" s="11">
         <v>3472</v>
       </c>
-      <c r="I6" s="12" t="s">
+      <c r="I6" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="J6" s="12">
-        <v>1</v>
-      </c>
-      <c r="K6" s="12" t="s">
+      <c r="J6" s="11">
+        <v>1</v>
+      </c>
+      <c r="K6" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="L6" s="12">
+      <c r="L6" s="11">
         <v>10001</v>
       </c>
-      <c r="M6" s="13"/>
-      <c r="N6" s="13"/>
-      <c r="O6" s="14"/>
+      <c r="M6" s="12"/>
+      <c r="N6" s="12"/>
+      <c r="O6" s="13"/>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A7" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="12" t="s">
+      <c r="A7" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="D7" s="12" t="s">
+      <c r="D7" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="E7" s="12"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="12">
+      <c r="E7" s="11"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="11">
         <v>3947</v>
       </c>
-      <c r="H7" s="12">
+      <c r="H7" s="11">
         <v>3947</v>
       </c>
-      <c r="I7" s="12" t="s">
+      <c r="I7" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="J7" s="12">
-        <v>1</v>
-      </c>
-      <c r="K7" s="12" t="s">
+      <c r="J7" s="11">
+        <v>1</v>
+      </c>
+      <c r="K7" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="L7" s="12">
+      <c r="L7" s="11">
         <v>10001</v>
       </c>
-      <c r="M7" s="13"/>
-      <c r="N7" s="13"/>
-      <c r="O7" s="14"/>
+      <c r="M7" s="12"/>
+      <c r="N7" s="12"/>
+      <c r="O7" s="13"/>
     </row>
     <row r="8" spans="1:27" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" s="11" t="s">
+      <c r="A8" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="E8" s="12"/>
-      <c r="F8" s="15"/>
-      <c r="G8" s="15">
+      <c r="E8" s="11"/>
+      <c r="F8" s="14"/>
+      <c r="G8" s="14">
         <v>19030701</v>
       </c>
-      <c r="H8" s="15">
+      <c r="H8" s="14">
         <v>19030701</v>
       </c>
-      <c r="I8" s="12" t="s">
+      <c r="I8" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="J8" s="12">
-        <v>1</v>
-      </c>
-      <c r="K8" s="12" t="s">
+      <c r="J8" s="11">
+        <v>1</v>
+      </c>
+      <c r="K8" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="L8" s="12">
+      <c r="L8" s="11">
         <v>4001</v>
       </c>
-      <c r="M8" s="13"/>
-      <c r="N8" s="13"/>
-      <c r="O8" s="14"/>
-      <c r="R8" s="18" t="s">
+      <c r="M8" s="12"/>
+      <c r="N8" s="12"/>
+      <c r="O8" s="13"/>
+      <c r="R8" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="S8" s="18"/>
-      <c r="T8" s="18"/>
-      <c r="U8" s="18"/>
-      <c r="V8" s="18"/>
-      <c r="W8" s="18"/>
-      <c r="X8" s="18"/>
-      <c r="Y8" s="18"/>
-      <c r="Z8" s="18"/>
-      <c r="AA8" s="18"/>
+      <c r="S8" s="17"/>
+      <c r="T8" s="17"/>
+      <c r="U8" s="17"/>
+      <c r="V8" s="17"/>
+      <c r="W8" s="17"/>
+      <c r="X8" s="17"/>
+      <c r="Y8" s="17"/>
+      <c r="Z8" s="17"/>
+      <c r="AA8" s="17"/>
     </row>
     <row r="9" spans="1:27" ht="26.85" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" s="11" t="s">
+      <c r="A9" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="D9" s="12" t="s">
+      <c r="D9" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="E9" s="12"/>
-      <c r="F9" s="15"/>
-      <c r="G9" s="15">
+      <c r="E9" s="11"/>
+      <c r="F9" s="14"/>
+      <c r="G9" s="14">
         <v>12</v>
       </c>
-      <c r="H9" s="15">
+      <c r="H9" s="14">
         <v>12</v>
       </c>
-      <c r="I9" s="12" t="s">
+      <c r="I9" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="J9" s="12">
-        <v>1</v>
-      </c>
-      <c r="K9" s="12" t="s">
+      <c r="J9" s="11">
+        <v>1</v>
+      </c>
+      <c r="K9" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="L9" s="12">
+      <c r="L9" s="11">
         <v>4002</v>
       </c>
-      <c r="M9" s="13"/>
-      <c r="N9" s="13"/>
-      <c r="O9" s="14"/>
-      <c r="R9" s="18" t="s">
+      <c r="M9" s="12"/>
+      <c r="N9" s="12"/>
+      <c r="O9" s="13"/>
+      <c r="R9" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="S9" s="18"/>
-      <c r="T9" s="18"/>
-      <c r="U9" s="18"/>
-      <c r="V9" s="18"/>
-      <c r="W9" s="18"/>
-      <c r="X9" s="18"/>
-      <c r="Y9" s="18"/>
-      <c r="Z9" s="18"/>
-      <c r="AA9" s="18"/>
+      <c r="S9" s="17"/>
+      <c r="T9" s="17"/>
+      <c r="U9" s="17"/>
+      <c r="V9" s="17"/>
+      <c r="W9" s="17"/>
+      <c r="X9" s="17"/>
+      <c r="Y9" s="17"/>
+      <c r="Z9" s="17"/>
+      <c r="AA9" s="17"/>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A10" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" s="11" t="s">
+      <c r="A10" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="D10" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="E10" s="12"/>
-      <c r="F10" s="15"/>
-      <c r="G10" s="15">
+      <c r="E10" s="11"/>
+      <c r="F10" s="14"/>
+      <c r="G10" s="14">
         <v>121415</v>
       </c>
-      <c r="H10" s="15">
-        <v>15</v>
-      </c>
-      <c r="I10" s="12" t="s">
+      <c r="H10" s="14">
+        <v>15</v>
+      </c>
+      <c r="I10" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="J10" s="12">
-        <v>1</v>
-      </c>
-      <c r="K10" s="12" t="s">
+      <c r="J10" s="11">
+        <v>1</v>
+      </c>
+      <c r="K10" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="L10" s="12">
+      <c r="L10" s="11">
         <v>4002</v>
       </c>
-      <c r="M10" s="13"/>
-      <c r="N10" s="13"/>
-      <c r="O10" s="14"/>
+      <c r="M10" s="12"/>
+      <c r="N10" s="12"/>
+      <c r="O10" s="13"/>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A11" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" s="11" t="s">
+      <c r="A11" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="D11" s="12" t="s">
+      <c r="D11" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="12">
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11">
         <v>233456974</v>
       </c>
-      <c r="H11" s="12">
-        <v>1</v>
-      </c>
-      <c r="I11" s="12" t="s">
+      <c r="H11" s="11">
+        <v>1</v>
+      </c>
+      <c r="I11" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="J11" s="12">
-        <v>1</v>
-      </c>
-      <c r="K11" s="12" t="s">
+      <c r="J11" s="11">
+        <v>1</v>
+      </c>
+      <c r="K11" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="L11" s="12">
+      <c r="L11" s="11">
         <v>4001</v>
       </c>
-      <c r="M11" s="13"/>
-      <c r="N11" s="13"/>
-      <c r="O11" s="14"/>
+      <c r="M11" s="12"/>
+      <c r="N11" s="12"/>
+      <c r="O11" s="13"/>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A12" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" s="11" t="s">
+      <c r="A12" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="D12" s="12" t="s">
+      <c r="D12" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="E12" s="12"/>
-      <c r="F12" s="15"/>
-      <c r="G12" s="15">
+      <c r="E12" s="11"/>
+      <c r="F12" s="14"/>
+      <c r="G12" s="14">
         <v>855276</v>
       </c>
-      <c r="H12" s="15">
+      <c r="H12" s="14">
         <v>855276</v>
       </c>
-      <c r="I12" s="12" t="s">
+      <c r="I12" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="J12" s="12">
-        <v>1</v>
-      </c>
-      <c r="K12" s="12" t="s">
+      <c r="J12" s="11">
+        <v>1</v>
+      </c>
+      <c r="K12" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="L12" s="12">
+      <c r="L12" s="11">
         <v>4004</v>
       </c>
-      <c r="M12" s="13"/>
-      <c r="N12" s="13"/>
-      <c r="O12" s="14"/>
+      <c r="M12" s="12"/>
+      <c r="N12" s="12"/>
+      <c r="O12" s="13"/>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A13" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C13" s="11" t="s">
+      <c r="A13" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="12" t="s">
+      <c r="D13" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="E13" s="12"/>
-      <c r="F13" s="15"/>
-      <c r="G13" s="15">
+      <c r="E13" s="11"/>
+      <c r="F13" s="14"/>
+      <c r="G13" s="14">
         <v>855278</v>
       </c>
-      <c r="H13" s="15">
+      <c r="H13" s="14">
         <v>855278</v>
       </c>
-      <c r="I13" s="12" t="s">
+      <c r="I13" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="J13" s="12">
-        <v>1</v>
-      </c>
-      <c r="K13" s="12" t="s">
+      <c r="J13" s="11">
+        <v>1</v>
+      </c>
+      <c r="K13" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="L13" s="12">
+      <c r="L13" s="11">
         <v>4004</v>
       </c>
-      <c r="M13" s="13"/>
-      <c r="N13" s="13"/>
-      <c r="O13" s="14"/>
+      <c r="M13" s="12"/>
+      <c r="N13" s="12"/>
+      <c r="O13" s="13"/>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A14" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C14" s="11" t="s">
+      <c r="A14" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="D14" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="E14" s="12"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="12">
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11">
         <v>173456975</v>
       </c>
-      <c r="H14" s="12">
-        <v>1</v>
-      </c>
-      <c r="I14" s="12" t="s">
+      <c r="H14" s="11">
+        <v>1</v>
+      </c>
+      <c r="I14" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="J14" s="12">
-        <v>1</v>
-      </c>
-      <c r="K14" s="12" t="s">
+      <c r="J14" s="11">
+        <v>1</v>
+      </c>
+      <c r="K14" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="L14" s="12">
+      <c r="L14" s="11">
         <v>4001</v>
       </c>
-      <c r="M14" s="13"/>
-      <c r="N14" s="13"/>
-      <c r="O14" s="14"/>
+      <c r="M14" s="12"/>
+      <c r="N14" s="12"/>
+      <c r="O14" s="13"/>
     </row>
     <row r="15" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15" s="11" t="s">
+      <c r="A15" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="D15" s="12" t="s">
+      <c r="D15" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="E15" s="12"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="12">
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11">
         <v>23222</v>
       </c>
-      <c r="H15" s="12">
-        <v>1</v>
-      </c>
-      <c r="I15" s="12" t="s">
+      <c r="H15" s="11">
+        <v>1</v>
+      </c>
+      <c r="I15" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="J15" s="12">
-        <v>1</v>
-      </c>
-      <c r="K15" s="12" t="s">
+      <c r="J15" s="11">
+        <v>1</v>
+      </c>
+      <c r="K15" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="L15" s="12">
+      <c r="L15" s="11">
         <v>4001</v>
       </c>
-      <c r="M15" s="13"/>
-      <c r="N15" s="13"/>
-      <c r="O15" s="17" t="s">
+      <c r="M15" s="12"/>
+      <c r="N15" s="12"/>
+      <c r="O15" s="16" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A16" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B16" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C16" s="11" t="s">
+      <c r="A16" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="D16" s="12" t="s">
+      <c r="D16" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="E16" s="12"/>
-      <c r="F16" s="12"/>
-      <c r="G16" s="12">
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="11">
         <v>17344</v>
       </c>
-      <c r="H16" s="12">
-        <v>1</v>
-      </c>
-      <c r="I16" s="12" t="s">
+      <c r="H16" s="11">
+        <v>1</v>
+      </c>
+      <c r="I16" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="J16" s="12">
-        <v>1</v>
-      </c>
-      <c r="K16" s="12" t="s">
+      <c r="J16" s="11">
+        <v>1</v>
+      </c>
+      <c r="K16" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="L16" s="12">
+      <c r="L16" s="11">
         <v>4001</v>
       </c>
-      <c r="M16" s="13"/>
-      <c r="N16" s="13"/>
-      <c r="O16" s="14"/>
+      <c r="M16" s="12"/>
+      <c r="N16" s="12"/>
+      <c r="O16" s="13"/>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A17" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B17" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C17" s="11" t="s">
+      <c r="A17" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="D17" s="12" t="s">
+      <c r="D17" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="E17" s="12"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="12">
+      <c r="E17" s="11"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="11">
         <v>17321</v>
       </c>
-      <c r="H17" s="12">
-        <v>1</v>
-      </c>
-      <c r="I17" s="12" t="s">
+      <c r="H17" s="11">
+        <v>1</v>
+      </c>
+      <c r="I17" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="J17" s="12">
-        <v>1</v>
-      </c>
-      <c r="K17" s="12" t="s">
+      <c r="J17" s="11">
+        <v>1</v>
+      </c>
+      <c r="K17" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="L17" s="12">
+      <c r="L17" s="11">
         <v>4001</v>
       </c>
-      <c r="M17" s="13"/>
-      <c r="N17" s="13"/>
-      <c r="O17" s="14"/>
+      <c r="M17" s="12"/>
+      <c r="N17" s="12"/>
+      <c r="O17" s="13"/>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A18" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D18" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="E18" s="11"/>
+      <c r="F18" s="14"/>
+      <c r="G18" s="19">
+        <v>2428744</v>
+      </c>
+      <c r="H18" s="14">
+        <v>655276</v>
+      </c>
+      <c r="I18" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="J18" s="11">
+        <v>1</v>
+      </c>
+      <c r="K18" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="L18" s="11">
+        <v>4004</v>
+      </c>
+      <c r="M18" s="12"/>
+      <c r="N18" s="12"/>
+      <c r="O18" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="R8:AA8"/>
     <mergeCell ref="R9:AA9"/>
   </mergeCells>
-  <conditionalFormatting sqref="G1:G1048576">
-    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
+  <conditionalFormatting sqref="G1:G17 G19:G1048576">
+    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G8:G10 G3 G12:G13">
-    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H8:H10 H3 H12:H13">
-    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H18">
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/prizmer/static/excel/heat_template_for_load.xlsx
+++ b/prizmer/static/excel/heat_template_for_load.xlsx
@@ -1,31 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Web-prizmer\wui3\prizmer\static\excel\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{135604E8-1EA0-44C8-B542-53BE444206F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
+  <fileVersion appName="Calc" lowestEdited="7"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="13860" yWindow="0" windowWidth="23640" windowHeight="17400" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Heat_1" sheetId="1" r:id="rId1"/>
+    <sheet name="Heat_1" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0" iterateDelta="0"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0"/>
+  <extLst>
+    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:v2="http://schemas.openxmlformats.org/spreadsheetml/2006/main/v2" mc:Ignorable="v2">
   <authors>
     <author>&lt;анонимный&gt;</author>
   </authors>
   <commentList>
-    <comment ref="O15" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="O15" authorId="0">
       <text>
         <r>
           <rPr>
@@ -34,171 +34,195 @@
             <family val="2"/>
             <charset val="204"/>
           </rPr>
-          <t>Да — будут создаваться 4 импульсных канала считывания данных</t>
+          <t xml:space="preserve">Да — будут создаваться 4 импульсных канала считывания данных</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>15</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>11</xdr:row>
+                <xdr:rowOff>1</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>16</xdr:col>
+                <xdr:colOff>42</xdr:colOff>
+                <xdr:row>15</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="61">
-  <si>
-    <t>Населенный пункт</t>
-  </si>
-  <si>
-    <t>Наименование улицы</t>
-  </si>
-  <si>
-    <t>Наименование дома</t>
-  </si>
-  <si>
-    <t>Квартира</t>
-  </si>
-  <si>
-    <t>Идентификатор АСКУЭ</t>
-  </si>
-  <si>
-    <t>Сетевой номер теплосчетчика HEX</t>
-  </si>
-  <si>
-    <t>Номер счётчика заводской</t>
-  </si>
-  <si>
-    <t>Номер в сети</t>
-  </si>
-  <si>
-    <t>Тип счётчика</t>
-  </si>
-  <si>
-    <t>ТТ</t>
-  </si>
-  <si>
-    <t>ip adress</t>
-  </si>
-  <si>
-    <t>ip port</t>
-  </si>
-  <si>
-    <t>Группа</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="63">
+  <si>
+    <t xml:space="preserve">Населенный пункт</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Наименование улицы</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Наименование дома</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Квартира</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Идентификатор АСКУЭ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Сетевой номер теплосчетчика HEX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Номер счётчика заводской</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Номер в сети</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Тип счётчика</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ТТ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ip adress</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ip port</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Группа</t>
   </si>
   <si>
     <t xml:space="preserve">Стояк </t>
   </si>
   <si>
-    <t>Дополнительные данные</t>
-  </si>
-  <si>
-    <t>г.Москва</t>
-  </si>
-  <si>
-    <t>ЖК "Московский"</t>
-  </si>
-  <si>
-    <t>Корпус 1</t>
-  </si>
-  <si>
-    <t>Квартира 0001</t>
-  </si>
-  <si>
-    <t>Danfoss SonoSelect</t>
-  </si>
-  <si>
-    <t>172.40.40.52</t>
-  </si>
-  <si>
-    <t>БКФН 403 (4.1.5)</t>
-  </si>
-  <si>
-    <t>Пульсар Теплосчётчик</t>
-  </si>
-  <si>
-    <t>192.168.15.78</t>
-  </si>
-  <si>
-    <t>Корпус 13</t>
-  </si>
-  <si>
-    <t>Квартира 0045</t>
-  </si>
-  <si>
-    <t>2e</t>
-  </si>
-  <si>
-    <t>01774391</t>
-  </si>
-  <si>
-    <t>Эльф 1.08</t>
-  </si>
-  <si>
-    <t>192.168.23.113</t>
-  </si>
-  <si>
-    <t>Квартира 0046</t>
-  </si>
-  <si>
-    <t>2f</t>
-  </si>
-  <si>
-    <t>01777072</t>
-  </si>
-  <si>
-    <t>Корпус 3</t>
-  </si>
-  <si>
-    <t>Квартира 0005</t>
-  </si>
-  <si>
-    <t>192.168.23.33</t>
-  </si>
-  <si>
-    <t>Квартира 0006</t>
-  </si>
-  <si>
-    <t>Корпус 5</t>
-  </si>
-  <si>
-    <t>Квартира 0125</t>
-  </si>
-  <si>
-    <t>Пульс СТК Теплосчётчик</t>
-  </si>
-  <si>
-    <t>172.30.0.26</t>
-  </si>
-  <si>
-    <t>*Нумерация квартир должна содержать нули, чтобы все числа имели одинаковый формат, иначе будут проблемы с сортировкой, лишние пробелы в наименовании так же могут сбить сортировку</t>
-  </si>
-  <si>
-    <t>ЭкоНом Теплосчётчик</t>
-  </si>
-  <si>
-    <t>172.30.0.27</t>
-  </si>
-  <si>
-    <t>**Для приборов Саяны так же необходимо создать bat-файлы для опроса счётчиков через ретрансляторы и АРСУ</t>
+    <t xml:space="preserve">Дополнительные данные</t>
+  </si>
+  <si>
+    <t xml:space="preserve">г.Москва</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ЖК "Московский"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Корпус 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Квартира 0001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Danfoss SonoSelect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">172.40.40.52</t>
+  </si>
+  <si>
+    <t xml:space="preserve">БКФН 403 (4.1.5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Пульсар Теплосчётчик</t>
+  </si>
+  <si>
+    <t xml:space="preserve">192.168.15.78</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Корпус 13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Квартира 0045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2e</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01774391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Эльф 1.08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">192.168.23.113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Квартира 0046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2f</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01777072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Корпус 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Квартира 0005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sayany</t>
+  </si>
+  <si>
+    <t xml:space="preserve">192.168.23.33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Квартира 0006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Корпус 5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Квартира 0125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Пульс СТК Теплосчётчик</t>
+  </si>
+  <si>
+    <t xml:space="preserve">172.30.0.26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">*Нумерация квартир должна содержать нули, чтобы все числа имели одинаковый формат, иначе будут проблемы с сортировкой, лишние пробелы в наименовании так же могут сбить сортировку</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ЭкоНом Теплосчётчик</t>
+  </si>
+  <si>
+    <t xml:space="preserve">172.30.0.27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">**Для приборов Саяны так же необходимо создать bat-файлы для опроса счётчиков через ретрансляторы и АРСУ</t>
   </si>
   <si>
     <t xml:space="preserve">Декаст Теплосчётчик </t>
   </si>
   <si>
-    <t>Danfoss SonoMeter-500</t>
-  </si>
-  <si>
-    <t>Пульсар IoT Тепло-объем</t>
-  </si>
-  <si>
-    <t>Пульсар IoT Тепло-энергия</t>
-  </si>
-  <si>
-    <t>ВКТ9</t>
-  </si>
-  <si>
-    <t>Корпус 7</t>
-  </si>
-  <si>
-    <t>Квартира 0111</t>
+    <t xml:space="preserve">Danfoss SonoMeter-500</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Пульсар IoT Тепло-объем</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Пульсар IoT Тепло-энергия</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ВКТ9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Корпус 7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Квартира 0111</t>
   </si>
   <si>
     <t xml:space="preserve">Теплосчётчик Ридан РУТ-01 </t>
@@ -207,41 +231,70 @@
     <t xml:space="preserve"> да</t>
   </si>
   <si>
-    <t>Корпус 32</t>
-  </si>
-  <si>
-    <t>Квартира 0201</t>
-  </si>
-  <si>
-    <t>ВЗЛЕТ ТСР-М ТСРВ-043</t>
-  </si>
-  <si>
-    <t>ВЗЛЕТ ТСР-М ТСРВ-024М</t>
-  </si>
-  <si>
-    <t>Sayany</t>
-  </si>
-  <si>
-    <t>Квартира 093</t>
-  </si>
-  <si>
-    <t>Пульсар Холодосчётчик</t>
+    <t xml:space="preserve">Корпус 32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Квартира 0201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ВЗЛЕТ ТСР-М ТСРВ-043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ВЗЛЕТ ТСР-М ТСРВ-024М</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Квартира 093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Пульсар Холодосчётчик</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Квартира 003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Пульсар 405 Теплосчётчик</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="000"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00"/>
+    <numFmt numFmtId="166" formatCode="000"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="204"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
@@ -251,7 +304,7 @@
       <charset val="1"/>
     </font>
     <font>
-      <b/>
+      <b val="true"/>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
@@ -259,7 +312,7 @@
       <charset val="204"/>
     </font>
     <font>
-      <b/>
+      <b val="true"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
@@ -278,10 +331,6 @@
       <name val="Arial"/>
       <family val="2"/>
       <charset val="204"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="4">
@@ -305,147 +354,173 @@
     </fill>
   </fills>
   <borders count="6">
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thick">
-        <color auto="1"/>
-      </left>
-      <right style="thick">
-        <color auto="1"/>
-      </right>
-      <top style="thick">
-        <color auto="1"/>
-      </top>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thick"/>
+      <right style="thick"/>
+      <top style="thick"/>
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="hair">
-        <color auto="1"/>
-      </left>
-      <right style="hair">
-        <color auto="1"/>
-      </right>
-      <top style="hair">
-        <color auto="1"/>
-      </top>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="hair"/>
+      <right style="hair"/>
+      <top style="hair"/>
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thick">
-        <color auto="1"/>
-      </left>
-      <right style="thick">
-        <color auto="1"/>
-      </right>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thick"/>
+      <right style="thick"/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="medium"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+  <cellStyleXfs count="22">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="20">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="justify"/>
-    </xf>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="justify" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="false" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="4" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="5" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="4" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
-  <cellStyles count="3">
-    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Обычный 2" xfId="2" xr:uid="{AC3BC87D-910B-4CD8-A453-B327BA67F137}"/>
-    <cellStyle name="Обычный 8" xfId="1" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
+  <cellStyles count="8">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
+    <cellStyle name="Обычный 2" xfId="20"/>
+    <cellStyle name="Обычный 8" xfId="21"/>
   </cellStyles>
   <dxfs count="4">
     <dxf>
@@ -489,7 +564,6 @@
       </fill>
     </dxf>
   </dxfs>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -548,29 +622,13 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF333333"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="LibreOffice">
       <a:dk1>
@@ -612,14 +670,14 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Arial"/>
-        <a:ea typeface="DejaVu Sans"/>
-        <a:cs typeface="DejaVu Sans"/>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Arial"/>
-        <a:ea typeface="DejaVu Sans"/>
-        <a:cs typeface="DejaVu Sans"/>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme>
@@ -672,30 +730,31 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AA18"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:AA19"/>
+  <sheetFormatPr defaultColWidth="8.71484375" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16.85546875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="10.28515625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="16.5703125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="11.7109375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="12" style="1" customWidth="1"/>
-    <col min="8" max="8" width="10.42578125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="26" style="1" customWidth="1"/>
-    <col min="10" max="10" width="5.140625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="18.28515625" style="1" customWidth="1"/>
-    <col min="15" max="15" width="18.140625" style="1" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="16.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="10.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="16.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="11.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="10.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="5.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="18.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="18.14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="75" x14ac:dyDescent="0.25">
+    <row r="1" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -742,7 +801,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="10" t="s">
         <v>15</v>
       </c>
@@ -757,29 +816,29 @@
       </c>
       <c r="E2" s="11"/>
       <c r="F2" s="11"/>
-      <c r="G2" s="11">
+      <c r="G2" s="11" t="n">
         <v>173456974</v>
       </c>
-      <c r="H2" s="11">
+      <c r="H2" s="11" t="n">
         <v>1</v>
       </c>
       <c r="I2" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="J2" s="11">
+      <c r="J2" s="11" t="n">
         <v>1</v>
       </c>
       <c r="K2" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="L2" s="11">
+      <c r="L2" s="11" t="n">
         <v>4001</v>
       </c>
       <c r="M2" s="12"/>
       <c r="N2" s="12"/>
       <c r="O2" s="13"/>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="10" t="s">
         <v>15</v>
       </c>
@@ -794,29 +853,29 @@
       </c>
       <c r="E3" s="11"/>
       <c r="F3" s="14"/>
-      <c r="G3" s="14">
+      <c r="G3" s="14" t="n">
         <v>655276</v>
       </c>
-      <c r="H3" s="14">
+      <c r="H3" s="14" t="n">
         <v>655276</v>
       </c>
       <c r="I3" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="J3" s="11">
+      <c r="J3" s="11" t="n">
         <v>1</v>
       </c>
       <c r="K3" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="L3" s="11">
+      <c r="L3" s="11" t="n">
         <v>4004</v>
       </c>
       <c r="M3" s="12"/>
       <c r="N3" s="12"/>
       <c r="O3" s="13"/>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
         <v>15</v>
       </c>
@@ -836,26 +895,26 @@
       <c r="G4" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="H4" s="11">
+      <c r="H4" s="11" t="n">
         <v>46</v>
       </c>
       <c r="I4" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="J4" s="11">
+      <c r="J4" s="11" t="n">
         <v>1</v>
       </c>
       <c r="K4" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="L4" s="11">
+      <c r="L4" s="11" t="n">
         <v>4001</v>
       </c>
       <c r="M4" s="12"/>
       <c r="N4" s="12"/>
       <c r="O4" s="13"/>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
         <v>15</v>
       </c>
@@ -875,26 +934,26 @@
       <c r="G5" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="H5" s="11">
+      <c r="H5" s="11" t="n">
         <v>47</v>
       </c>
       <c r="I5" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="J5" s="11">
+      <c r="J5" s="11" t="n">
         <v>1</v>
       </c>
       <c r="K5" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="L5" s="11">
+      <c r="L5" s="11" t="n">
         <v>4001</v>
       </c>
       <c r="M5" s="12"/>
       <c r="N5" s="12"/>
       <c r="O5" s="13"/>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
         <v>15</v>
       </c>
@@ -909,29 +968,29 @@
       </c>
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
-      <c r="G6" s="11">
+      <c r="G6" s="11" t="n">
         <v>3472</v>
       </c>
-      <c r="H6" s="11">
+      <c r="H6" s="11" t="n">
         <v>3472</v>
       </c>
       <c r="I6" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="J6" s="11">
+        <v>35</v>
+      </c>
+      <c r="J6" s="11" t="n">
         <v>1</v>
       </c>
       <c r="K6" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="L6" s="11">
+        <v>36</v>
+      </c>
+      <c r="L6" s="11" t="n">
         <v>10001</v>
       </c>
       <c r="M6" s="12"/>
       <c r="N6" s="12"/>
       <c r="O6" s="13"/>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
         <v>15</v>
       </c>
@@ -942,33 +1001,33 @@
         <v>33</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E7" s="11"/>
       <c r="F7" s="11"/>
-      <c r="G7" s="11">
+      <c r="G7" s="11" t="n">
         <v>3947</v>
       </c>
-      <c r="H7" s="11">
+      <c r="H7" s="11" t="n">
         <v>3947</v>
       </c>
       <c r="I7" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="J7" s="11">
+        <v>35</v>
+      </c>
+      <c r="J7" s="11" t="n">
         <v>1</v>
       </c>
       <c r="K7" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="L7" s="11">
+        <v>36</v>
+      </c>
+      <c r="L7" s="11" t="n">
         <v>10001</v>
       </c>
       <c r="M7" s="12"/>
       <c r="N7" s="12"/>
       <c r="O7" s="13"/>
     </row>
-    <row r="8" spans="1:27" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="s">
         <v>15</v>
       </c>
@@ -976,48 +1035,48 @@
         <v>16</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E8" s="11"/>
       <c r="F8" s="14"/>
-      <c r="G8" s="14">
+      <c r="G8" s="14" t="n">
         <v>19030701</v>
       </c>
-      <c r="H8" s="14">
+      <c r="H8" s="14" t="n">
         <v>19030701</v>
       </c>
       <c r="I8" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="J8" s="11">
+        <v>40</v>
+      </c>
+      <c r="J8" s="11" t="n">
         <v>1</v>
       </c>
       <c r="K8" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="L8" s="11">
+        <v>41</v>
+      </c>
+      <c r="L8" s="11" t="n">
         <v>4001</v>
       </c>
       <c r="M8" s="12"/>
       <c r="N8" s="12"/>
       <c r="O8" s="13"/>
-      <c r="R8" s="17" t="s">
-        <v>41</v>
-      </c>
-      <c r="S8" s="17"/>
-      <c r="T8" s="17"/>
-      <c r="U8" s="17"/>
-      <c r="V8" s="17"/>
-      <c r="W8" s="17"/>
-      <c r="X8" s="17"/>
-      <c r="Y8" s="17"/>
-      <c r="Z8" s="17"/>
-      <c r="AA8" s="17"/>
-    </row>
-    <row r="9" spans="1:27" ht="26.85" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R8" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="S8" s="16"/>
+      <c r="T8" s="16"/>
+      <c r="U8" s="16"/>
+      <c r="V8" s="16"/>
+      <c r="W8" s="16"/>
+      <c r="X8" s="16"/>
+      <c r="Y8" s="16"/>
+      <c r="Z8" s="16"/>
+      <c r="AA8" s="16"/>
+    </row>
+    <row r="9" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
         <v>15</v>
       </c>
@@ -1025,48 +1084,48 @@
         <v>16</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E9" s="11"/>
       <c r="F9" s="14"/>
-      <c r="G9" s="14">
+      <c r="G9" s="14" t="n">
         <v>12</v>
       </c>
-      <c r="H9" s="14">
+      <c r="H9" s="14" t="n">
         <v>12</v>
       </c>
       <c r="I9" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="J9" s="11">
+        <v>43</v>
+      </c>
+      <c r="J9" s="11" t="n">
         <v>1</v>
       </c>
       <c r="K9" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="L9" s="11">
+        <v>44</v>
+      </c>
+      <c r="L9" s="11" t="n">
         <v>4002</v>
       </c>
       <c r="M9" s="12"/>
       <c r="N9" s="12"/>
       <c r="O9" s="13"/>
-      <c r="R9" s="17" t="s">
-        <v>44</v>
-      </c>
-      <c r="S9" s="17"/>
-      <c r="T9" s="17"/>
-      <c r="U9" s="17"/>
-      <c r="V9" s="17"/>
-      <c r="W9" s="17"/>
-      <c r="X9" s="17"/>
-      <c r="Y9" s="17"/>
-      <c r="Z9" s="17"/>
-      <c r="AA9" s="17"/>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="R9" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="S9" s="16"/>
+      <c r="T9" s="16"/>
+      <c r="U9" s="16"/>
+      <c r="V9" s="16"/>
+      <c r="W9" s="16"/>
+      <c r="X9" s="16"/>
+      <c r="Y9" s="16"/>
+      <c r="Z9" s="16"/>
+      <c r="AA9" s="16"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="s">
         <v>15</v>
       </c>
@@ -1074,36 +1133,36 @@
         <v>16</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E10" s="11"/>
       <c r="F10" s="14"/>
-      <c r="G10" s="14">
+      <c r="G10" s="14" t="n">
         <v>121415</v>
       </c>
-      <c r="H10" s="14">
+      <c r="H10" s="14" t="n">
         <v>15</v>
       </c>
       <c r="I10" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="J10" s="11">
+        <v>46</v>
+      </c>
+      <c r="J10" s="11" t="n">
         <v>1</v>
       </c>
       <c r="K10" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="L10" s="11">
+        <v>44</v>
+      </c>
+      <c r="L10" s="11" t="n">
         <v>4002</v>
       </c>
       <c r="M10" s="12"/>
       <c r="N10" s="12"/>
       <c r="O10" s="13"/>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
         <v>15</v>
       </c>
@@ -1118,29 +1177,29 @@
       </c>
       <c r="E11" s="11"/>
       <c r="F11" s="11"/>
-      <c r="G11" s="11">
+      <c r="G11" s="11" t="n">
         <v>233456974</v>
       </c>
-      <c r="H11" s="11">
+      <c r="H11" s="11" t="n">
         <v>1</v>
       </c>
       <c r="I11" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="J11" s="11">
+        <v>47</v>
+      </c>
+      <c r="J11" s="11" t="n">
         <v>1</v>
       </c>
       <c r="K11" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="L11" s="11">
+      <c r="L11" s="11" t="n">
         <v>4001</v>
       </c>
       <c r="M11" s="12"/>
       <c r="N11" s="12"/>
       <c r="O11" s="13"/>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="10" t="s">
         <v>15</v>
       </c>
@@ -1155,29 +1214,29 @@
       </c>
       <c r="E12" s="11"/>
       <c r="F12" s="14"/>
-      <c r="G12" s="14">
+      <c r="G12" s="14" t="n">
         <v>855276</v>
       </c>
-      <c r="H12" s="14">
+      <c r="H12" s="14" t="n">
         <v>855276</v>
       </c>
       <c r="I12" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="J12" s="11">
+        <v>48</v>
+      </c>
+      <c r="J12" s="11" t="n">
         <v>1</v>
       </c>
       <c r="K12" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="L12" s="11">
+      <c r="L12" s="11" t="n">
         <v>4004</v>
       </c>
       <c r="M12" s="12"/>
       <c r="N12" s="12"/>
       <c r="O12" s="13"/>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="10" t="s">
         <v>15</v>
       </c>
@@ -1192,29 +1251,29 @@
       </c>
       <c r="E13" s="11"/>
       <c r="F13" s="14"/>
-      <c r="G13" s="14">
+      <c r="G13" s="14" t="n">
         <v>855278</v>
       </c>
-      <c r="H13" s="14">
+      <c r="H13" s="14" t="n">
         <v>855278</v>
       </c>
       <c r="I13" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="J13" s="11">
+        <v>49</v>
+      </c>
+      <c r="J13" s="11" t="n">
         <v>1</v>
       </c>
       <c r="K13" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="L13" s="11">
+      <c r="L13" s="11" t="n">
         <v>4004</v>
       </c>
       <c r="M13" s="12"/>
       <c r="N13" s="12"/>
       <c r="O13" s="13"/>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="10" t="s">
         <v>15</v>
       </c>
@@ -1229,29 +1288,29 @@
       </c>
       <c r="E14" s="11"/>
       <c r="F14" s="11"/>
-      <c r="G14" s="11">
+      <c r="G14" s="11" t="n">
         <v>173456975</v>
       </c>
-      <c r="H14" s="11">
+      <c r="H14" s="11" t="n">
         <v>1</v>
       </c>
       <c r="I14" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="J14" s="11">
+        <v>50</v>
+      </c>
+      <c r="J14" s="11" t="n">
         <v>1</v>
       </c>
       <c r="K14" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="L14" s="11">
+      <c r="L14" s="11" t="n">
         <v>4001</v>
       </c>
       <c r="M14" s="12"/>
       <c r="N14" s="12"/>
       <c r="O14" s="13"/>
     </row>
-    <row r="15" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="10" t="s">
         <v>15</v>
       </c>
@@ -1259,38 +1318,38 @@
         <v>16</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E15" s="11"/>
       <c r="F15" s="11"/>
-      <c r="G15" s="11">
+      <c r="G15" s="11" t="n">
         <v>23222</v>
       </c>
-      <c r="H15" s="11">
+      <c r="H15" s="11" t="n">
         <v>1</v>
       </c>
       <c r="I15" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="J15" s="11">
+        <v>53</v>
+      </c>
+      <c r="J15" s="11" t="n">
         <v>1</v>
       </c>
       <c r="K15" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="L15" s="11">
+      <c r="L15" s="11" t="n">
         <v>4001</v>
       </c>
       <c r="M15" s="12"/>
       <c r="N15" s="12"/>
-      <c r="O15" s="16" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="O15" s="17" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="10" t="s">
         <v>15</v>
       </c>
@@ -1298,36 +1357,36 @@
         <v>16</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E16" s="11"/>
       <c r="F16" s="11"/>
-      <c r="G16" s="11">
+      <c r="G16" s="11" t="n">
         <v>17344</v>
       </c>
-      <c r="H16" s="11">
+      <c r="H16" s="11" t="n">
         <v>1</v>
       </c>
       <c r="I16" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="J16" s="11">
+        <v>57</v>
+      </c>
+      <c r="J16" s="11" t="n">
         <v>1</v>
       </c>
       <c r="K16" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="L16" s="11">
+      <c r="L16" s="11" t="n">
         <v>4001</v>
       </c>
       <c r="M16" s="12"/>
       <c r="N16" s="12"/>
       <c r="O16" s="13"/>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="10" t="s">
         <v>15</v>
       </c>
@@ -1335,36 +1394,36 @@
         <v>16</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E17" s="11"/>
       <c r="F17" s="11"/>
-      <c r="G17" s="11">
+      <c r="G17" s="11" t="n">
         <v>17321</v>
       </c>
-      <c r="H17" s="11">
+      <c r="H17" s="11" t="n">
         <v>1</v>
       </c>
       <c r="I17" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="J17" s="11">
+        <v>58</v>
+      </c>
+      <c r="J17" s="11" t="n">
         <v>1</v>
       </c>
       <c r="K17" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="L17" s="11">
+      <c r="L17" s="11" t="n">
         <v>4001</v>
       </c>
       <c r="M17" s="12"/>
       <c r="N17" s="12"/>
       <c r="O17" s="13"/>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="10" t="s">
         <v>15</v>
       </c>
@@ -1379,47 +1438,89 @@
       </c>
       <c r="E18" s="11"/>
       <c r="F18" s="14"/>
-      <c r="G18" s="19">
+      <c r="G18" s="19" t="n">
         <v>2428744</v>
       </c>
-      <c r="H18" s="14">
+      <c r="H18" s="14" t="n">
         <v>655276</v>
       </c>
       <c r="I18" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="J18" s="11">
+      <c r="J18" s="11" t="n">
         <v>1</v>
       </c>
       <c r="K18" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="L18" s="11">
+      <c r="L18" s="11" t="n">
         <v>4004</v>
       </c>
       <c r="M18" s="12"/>
       <c r="N18" s="12"/>
       <c r="O18" s="13"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="D19" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="E19" s="11"/>
+      <c r="F19" s="14"/>
+      <c r="G19" s="19" t="n">
+        <v>2428743</v>
+      </c>
+      <c r="H19" s="19" t="n">
+        <v>2428743</v>
+      </c>
+      <c r="I19" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="J19" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="L19" s="11" t="n">
+        <v>4004</v>
+      </c>
+      <c r="M19" s="12"/>
+      <c r="N19" s="12"/>
+      <c r="O19" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="R8:AA8"/>
     <mergeCell ref="R9:AA9"/>
   </mergeCells>
-  <conditionalFormatting sqref="G1:G17 G19:G1048576">
-    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
+  <conditionalFormatting sqref="H18">
+    <cfRule type="duplicateValues" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G1:G17 G20:G1048576">
+    <cfRule type="duplicateValues" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G8:G10 G3 G12:G13">
-    <cfRule type="duplicateValues" dxfId="2" priority="5"/>
+    <cfRule type="duplicateValues" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H8:H10 H3 H12:H13">
-    <cfRule type="duplicateValues" dxfId="1" priority="6"/>
+    <cfRule type="duplicateValues" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H18">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
-  </conditionalFormatting>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <legacyDrawing r:id="rId1"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/prizmer/static/excel/heat_template_for_load.xlsx
+++ b/prizmer/static/excel/heat_template_for_load.xlsx
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="66">
   <si>
     <t xml:space="preserve">Населенный пункт</t>
   </si>
@@ -253,6 +253,15 @@
   </si>
   <si>
     <t xml:space="preserve">Пульсар 405 Теплосчётчик</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Корпус 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Квартира 017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вис.Т</t>
   </si>
 </sst>
 </file>
@@ -738,11 +747,11 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AA19"/>
+  <dimension ref="A1:AA20"/>
   <sheetFormatPr defaultColWidth="8.71484375" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="16.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="16.84"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="10.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="16.57"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="11.71"/>
@@ -1497,6 +1506,43 @@
       <c r="N19" s="12"/>
       <c r="O19" s="13"/>
     </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="D20" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="E20" s="11"/>
+      <c r="F20" s="14"/>
+      <c r="G20" s="19" t="n">
+        <v>2345</v>
+      </c>
+      <c r="H20" s="19" t="n">
+        <v>775</v>
+      </c>
+      <c r="I20" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="J20" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="L20" s="11" t="n">
+        <v>4004</v>
+      </c>
+      <c r="M20" s="12"/>
+      <c r="N20" s="12"/>
+      <c r="O20" s="13"/>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="R8:AA8"/>
@@ -1505,7 +1551,7 @@
   <conditionalFormatting sqref="H18">
     <cfRule type="duplicateValues" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G1:G17 G20:G1048576">
+  <conditionalFormatting sqref="G1:G17 G21:G1048576">
     <cfRule type="duplicateValues" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G8:G10 G3 G12:G13">

--- a/prizmer/static/excel/heat_template_for_load.xlsx
+++ b/prizmer/static/excel/heat_template_for_load.xlsx
@@ -261,7 +261,7 @@
     <t xml:space="preserve">Квартира 017</t>
   </si>
   <si>
-    <t xml:space="preserve">Вис.Т</t>
+    <t xml:space="preserve">Вис.Т-ТС</t>
   </si>
 </sst>
 </file>
@@ -273,7 +273,7 @@
     <numFmt numFmtId="165" formatCode="#,##0.00"/>
     <numFmt numFmtId="166" formatCode="000"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -339,6 +339,13 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
       <charset val="204"/>
     </font>
   </fonts>
@@ -439,7 +446,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -518,6 +525,10 @@
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="4" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1527,7 +1538,7 @@
       <c r="H20" s="19" t="n">
         <v>775</v>
       </c>
-      <c r="I20" s="11" t="s">
+      <c r="I20" s="20" t="s">
         <v>65</v>
       </c>
       <c r="J20" s="11" t="n">
